--- a/r4-ELGA-AustrianPatientSummary-55-56---create-examples-for-each-at-aps-profile/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-55-56---create-examples-for-each-at-aps-profile/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T12:31:41+00:00</t>
+    <t>2026-01-28T09:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1069,7 +1069,7 @@
     <t>Device.owner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -1169,7 +1169,7 @@
     <t>Device.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device)
 </t>
   </si>
   <si>
@@ -1499,7 +1499,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="59.90234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="64.109375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
